--- a/output/2026-09-07_00_Slovenia_Gorenjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-07_00_Slovenia_Gorenjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -662,10 +662,9 @@
           <t>(04) 583 43 00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verificato come punto vendita attivo, ma catena generalista fai-da-te/casa (vernici, elettrodomestici, giardino) con solo reparto utensileria - rilevanza B2B industriale marginale, da valutare priorità bassa; email generica non reperita</t>
+          <t>Verificato come punto vendita attivo, ma catena generalista fai-da-te/casa (vernici, elettrodomestici, giardino) con solo reparto utensileria - rilevanza B2B industriale marginale, da valutare priorità bassa; email generica non reperita [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
